--- a/data/Taller_DET_Agosto/Swap_max_production/elmo_data.xlsx
+++ b/data/Taller_DET_Agosto/Swap_max_production/elmo_data.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Agustin\Desktop\Elmo_battery_swapping_wt\data\Taller_DET_Agosto\Swap_costo_fijo_meta_carta_tiraje\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Agustin\Desktop\Elmo_infrastructure_NP\data\Taller_DET_Agosto\Swap_max_production\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E568D48-6EF5-4651-9BDC-A1B94EA2124E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB5B7CC4-35B0-44DE-935A-7D83DFEC7BAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" firstSheet="3" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LHD" sheetId="2" r:id="rId1"/>
@@ -2449,8 +2449,8 @@
         <v>59</v>
       </c>
       <c r="C3" s="8">
-        <f>2*35722</f>
-        <v>71444</v>
+        <f>35722</f>
+        <v>35722</v>
       </c>
       <c r="D3" s="14">
         <v>38221</v>
@@ -2465,7 +2465,7 @@
         <v>4389</v>
       </c>
       <c r="H3" s="15">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I3" s="15">
         <v>2</v>
@@ -2474,7 +2474,7 @@
         <v>2</v>
       </c>
       <c r="K3" s="8">
-        <v>2400</v>
+        <v>1200</v>
       </c>
     </row>
   </sheetData>
